--- a/results/광명금속/광명금속_valid_LSTM_(36,32)_first_window.xlsx
+++ b/results/광명금속/광명금속_valid_LSTM_(36,32)_first_window.xlsx
@@ -462,10 +462,10 @@
         <v>30.54</v>
       </c>
       <c r="C2" t="n">
-        <v>30.53999900817871</v>
+        <v>30.53999710083008</v>
       </c>
       <c r="D2" t="n">
-        <v>24.2646312713623</v>
+        <v>18.25867462158203</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         <v>31.44</v>
       </c>
       <c r="C3" t="n">
-        <v>31.44000053405762</v>
+        <v>31.44000244140625</v>
       </c>
       <c r="D3" t="n">
-        <v>23.87685966491699</v>
+        <v>23.52796363830566</v>
       </c>
     </row>
     <row r="4">
@@ -490,10 +490,10 @@
         <v>29.18</v>
       </c>
       <c r="C4" t="n">
-        <v>29.18000030517578</v>
+        <v>29.17999649047852</v>
       </c>
       <c r="D4" t="n">
-        <v>24.49203109741211</v>
+        <v>22.0163688659668</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         <v>26.52000045776367</v>
       </c>
       <c r="D5" t="n">
-        <v>26.23886489868164</v>
+        <v>23.61700248718262</v>
       </c>
     </row>
     <row r="6">
@@ -518,10 +518,10 @@
         <v>26.72</v>
       </c>
       <c r="C6" t="n">
-        <v>26.72000122070312</v>
+        <v>26.71999549865723</v>
       </c>
       <c r="D6" t="n">
-        <v>25.51615142822266</v>
+        <v>20.16515159606934</v>
       </c>
     </row>
     <row r="7">
@@ -532,10 +532,10 @@
         <v>26.58</v>
       </c>
       <c r="C7" t="n">
-        <v>26.57999992370605</v>
+        <v>26.57999610900879</v>
       </c>
       <c r="D7" t="n">
-        <v>25.62586784362793</v>
+        <v>19.94160842895508</v>
       </c>
     </row>
     <row r="8">
@@ -546,10 +546,10 @@
         <v>30.44</v>
       </c>
       <c r="C8" t="n">
-        <v>30.44000053405762</v>
+        <v>30.44000244140625</v>
       </c>
       <c r="D8" t="n">
-        <v>25.85740852355957</v>
+        <v>22.16409301757812</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>31.97999954223633</v>
       </c>
       <c r="D9" t="n">
-        <v>26.80032730102539</v>
+        <v>23.33013534545898</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         <v>33.56000137329102</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18700790405273</v>
+        <v>24.1016960144043</v>
       </c>
     </row>
     <row r="11">
@@ -591,7 +591,7 @@
         <v>32.43999862670898</v>
       </c>
       <c r="D11" t="n">
-        <v>27.87512397766113</v>
+        <v>18.64112091064453</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         <v>33.62</v>
       </c>
       <c r="C12" t="n">
-        <v>33.61999893188477</v>
+        <v>33.6199951171875</v>
       </c>
       <c r="D12" t="n">
-        <v>26.20019340515137</v>
+        <v>24.50583648681641</v>
       </c>
     </row>
     <row r="13">
@@ -619,7 +619,7 @@
         <v>30.93999862670898</v>
       </c>
       <c r="D13" t="n">
-        <v>23.97912406921387</v>
+        <v>19.84327125549316</v>
       </c>
     </row>
     <row r="14">
@@ -630,10 +630,10 @@
         <v>25.62</v>
       </c>
       <c r="C14" t="n">
-        <v>25.61999893188477</v>
+        <v>25.61999702453613</v>
       </c>
       <c r="D14" t="n">
-        <v>17.94871520996094</v>
+        <v>18.75099563598633</v>
       </c>
     </row>
     <row r="15">
@@ -647,7 +647,7 @@
         <v>6.139999866485596</v>
       </c>
       <c r="D15" t="n">
-        <v>12.26028442382812</v>
+        <v>13.61285972595215</v>
       </c>
     </row>
     <row r="16">
@@ -661,7 +661,7 @@
         <v>5.519999980926514</v>
       </c>
       <c r="D16" t="n">
-        <v>8.935885429382324</v>
+        <v>17.39118957519531</v>
       </c>
     </row>
     <row r="17">
@@ -675,7 +675,7 @@
         <v>5.659999847412109</v>
       </c>
       <c r="D17" t="n">
-        <v>7.700887203216553</v>
+        <v>18.1419563293457</v>
       </c>
     </row>
     <row r="18">
@@ -689,7 +689,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D18" t="n">
-        <v>11.2529821395874</v>
+        <v>16.8028450012207</v>
       </c>
     </row>
     <row r="19">
@@ -700,10 +700,10 @@
         <v>23.66</v>
       </c>
       <c r="C19" t="n">
-        <v>23.65999984741211</v>
+        <v>23.65999603271484</v>
       </c>
       <c r="D19" t="n">
-        <v>17.69706535339355</v>
+        <v>17.45012283325195</v>
       </c>
     </row>
     <row r="20">
@@ -717,7 +717,7 @@
         <v>24.47999954223633</v>
       </c>
       <c r="D20" t="n">
-        <v>21.72130966186523</v>
+        <v>18.06053924560547</v>
       </c>
     </row>
     <row r="21">
@@ -728,10 +728,10 @@
         <v>25.3</v>
       </c>
       <c r="C21" t="n">
-        <v>25.30000114440918</v>
+        <v>25.29999923706055</v>
       </c>
       <c r="D21" t="n">
-        <v>24.58523559570312</v>
+        <v>18.2085075378418</v>
       </c>
     </row>
     <row r="22">
@@ -742,10 +742,10 @@
         <v>25.06</v>
       </c>
       <c r="C22" t="n">
-        <v>25.05999946594238</v>
+        <v>25.05999755859375</v>
       </c>
       <c r="D22" t="n">
-        <v>26.24079895019531</v>
+        <v>19.19643402099609</v>
       </c>
     </row>
     <row r="23">
@@ -756,10 +756,10 @@
         <v>32.52</v>
       </c>
       <c r="C23" t="n">
-        <v>32.52000045776367</v>
+        <v>32.51999664306641</v>
       </c>
       <c r="D23" t="n">
-        <v>26.77082443237305</v>
+        <v>22.80800247192383</v>
       </c>
     </row>
     <row r="24">
@@ -770,10 +770,10 @@
         <v>26.24</v>
       </c>
       <c r="C24" t="n">
-        <v>26.23999977111816</v>
+        <v>26.2399959564209</v>
       </c>
       <c r="D24" t="n">
-        <v>27.06458282470703</v>
+        <v>20.90188980102539</v>
       </c>
     </row>
     <row r="25">
@@ -784,10 +784,10 @@
         <v>25.66</v>
       </c>
       <c r="C25" t="n">
-        <v>25.65999984741211</v>
+        <v>25.65999794006348</v>
       </c>
       <c r="D25" t="n">
-        <v>25.45065689086914</v>
+        <v>19.80489349365234</v>
       </c>
     </row>
     <row r="26">
@@ -801,7 +801,7 @@
         <v>21.05999946594238</v>
       </c>
       <c r="D26" t="n">
-        <v>24.69918441772461</v>
+        <v>18.30624771118164</v>
       </c>
     </row>
     <row r="27">
@@ -812,10 +812,10 @@
         <v>18.38</v>
       </c>
       <c r="C27" t="n">
-        <v>18.3799991607666</v>
+        <v>18.37999725341797</v>
       </c>
       <c r="D27" t="n">
-        <v>23.88037300109863</v>
+        <v>21.45015144348145</v>
       </c>
     </row>
     <row r="28">
@@ -829,7 +829,7 @@
         <v>18.11999893188477</v>
       </c>
       <c r="D28" t="n">
-        <v>25.01105690002441</v>
+        <v>21.87932205200195</v>
       </c>
     </row>
     <row r="29">
@@ -840,10 +840,10 @@
         <v>18.6</v>
       </c>
       <c r="C29" t="n">
-        <v>18.60000038146973</v>
+        <v>18.59999656677246</v>
       </c>
       <c r="D29" t="n">
-        <v>24.74263000488281</v>
+        <v>20.1151065826416</v>
       </c>
     </row>
     <row r="30">
@@ -857,7 +857,7 @@
         <v>18.11999893188477</v>
       </c>
       <c r="D30" t="n">
-        <v>24.49235725402832</v>
+        <v>23.5684700012207</v>
       </c>
     </row>
     <row r="31">
@@ -868,10 +868,10 @@
         <v>18.32</v>
       </c>
       <c r="C31" t="n">
-        <v>18.31999969482422</v>
+        <v>18.32000160217285</v>
       </c>
       <c r="D31" t="n">
-        <v>25.38231468200684</v>
+        <v>21.12070274353027</v>
       </c>
     </row>
     <row r="32">
@@ -882,10 +882,10 @@
         <v>18.42</v>
       </c>
       <c r="C32" t="n">
-        <v>18.42000007629395</v>
+        <v>18.41999816894531</v>
       </c>
       <c r="D32" t="n">
-        <v>25.52099227905273</v>
+        <v>18.37917518615723</v>
       </c>
     </row>
     <row r="33">
@@ -899,7 +899,7 @@
         <v>21.13999938964844</v>
       </c>
       <c r="D33" t="n">
-        <v>25.64393043518066</v>
+        <v>15.55431938171387</v>
       </c>
     </row>
   </sheetData>
